--- a/Sajjad data/by_country_and_state/USA/NC.xlsx
+++ b/Sajjad data/by_country_and_state/USA/NC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="445">
   <si>
     <t>Business Name</t>
   </si>
@@ -1283,6 +1283,69 @@
   </si>
   <si>
     <t>2026-10-25T04:20:27.035Z</t>
+  </si>
+  <si>
+    <t>Dental Now Connect</t>
+  </si>
+  <si>
+    <t>(910) 459-5748</t>
+  </si>
+  <si>
+    <t>330 Shipyard Blvd, Wilmington, NC 28412</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Now+Connect/data=!4m7!3m6!1s0x89aa1f547e6114f5:0x6993f7cc34e6f44c!8m2!3d34.1910919!4d-77.9398033!16s%2Fg%2F11nvh6cq8l!19sChIJ9RRhflQfqokRTPTmNMz3k2k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:09.788Z</t>
+  </si>
+  <si>
+    <t>Dr. Safia Azizi, DMD</t>
+  </si>
+  <si>
+    <t>(910) 332-0687</t>
+  </si>
+  <si>
+    <t>215 Racine Dr Ste 102, Wilmington, NC 28403</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Safia+Azizi,+DMD/data=!4m7!3m6!1s0x89a9f4c1669a7f89:0x32f88a6d87c5175e!8m2!3d34.2394239!4d-77.8648687!16s%2Fg%2F1tjt2t7g!19sChIJiX-aZsH0qYkRXhfFh22K-DI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:30.138Z</t>
+  </si>
+  <si>
+    <t>Brightly White</t>
+  </si>
+  <si>
+    <t>(910) 632-0266</t>
+  </si>
+  <si>
+    <t>3333 Wrightsville Ave Unit G123, Wilmington, NC 28403</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brightly+White/data=!4m7!3m6!1s0x28b512e5d05a3c61:0x7e0bd29f36f2175c!8m2!3d34.2234245!4d-77.9011535!16s%2Fg%2F11thpxfrt_!19sChIJYTxa0OUStSgRXBfyNp_SC34?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:48.932Z</t>
+  </si>
+  <si>
+    <t>Banta Susan K DDS</t>
+  </si>
+  <si>
+    <t>(910) 772-9770</t>
+  </si>
+  <si>
+    <t>1611 Doctors Cir, Wilmington, NC 28401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Banta+Susan+K+DDS/data=!4m7!3m6!1s0x89a9f589cae4462f:0xb22714d8b4f4689f!8m2!3d34.2060511!4d-77.9270785!16s%2Fg%2F1tt8d3s3!19sChIJL0bkyon1qYkRn2j0tNgUJ7I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:57.805Z</t>
   </si>
 </sst>
 </file>
@@ -1663,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4591,6 +4654,170 @@
         <v>423</v>
       </c>
     </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>424</v>
+      </c>
+      <c r="B72" t="s">
+        <v>425</v>
+      </c>
+      <c r="C72" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" t="s">
+        <v>426</v>
+      </c>
+      <c r="E72" t="s">
+        <v>390</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>51</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>427</v>
+      </c>
+      <c r="M72" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>429</v>
+      </c>
+      <c r="B73" t="s">
+        <v>430</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>431</v>
+      </c>
+      <c r="E73" t="s">
+        <v>390</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>432</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>51</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>433</v>
+      </c>
+      <c r="M73" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>435</v>
+      </c>
+      <c r="B74" t="s">
+        <v>436</v>
+      </c>
+      <c r="C74" t="s">
+        <v>143</v>
+      </c>
+      <c r="D74" t="s">
+        <v>437</v>
+      </c>
+      <c r="E74" t="s">
+        <v>390</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>261</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>438</v>
+      </c>
+      <c r="M74" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>440</v>
+      </c>
+      <c r="B75" t="s">
+        <v>441</v>
+      </c>
+      <c r="C75" t="s">
+        <v>179</v>
+      </c>
+      <c r="D75" t="s">
+        <v>442</v>
+      </c>
+      <c r="E75" t="s">
+        <v>390</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>43</v>
+      </c>
+      <c r="I75" t="s">
+        <v>340</v>
+      </c>
+      <c r="J75" t="s">
+        <v>51</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>443</v>
+      </c>
+      <c r="M75" t="s">
+        <v>444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
